--- a/data/employees/EMP092/AST-EMP092-06.xlsx
+++ b/data/employees/EMP092/AST-EMP092-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Budget Tracker - Jordan Nguyen (Finance)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jordan Nguyen | Role: Analyst | Location: Bengaluru | Date: 2025-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>73</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost Centre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Budget ($K)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Actual ($K)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Variance ($K)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC-1001 Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>66</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Customer escalation analysis. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC-1002 Operations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-120</v>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-6.7</v>
+        <v>82</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC-1003 R&amp;D</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>69</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Data quality remediation. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC-1004 IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>61</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Section 1: Fabric semantic model planning. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>66</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>94</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>96</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>92</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>83</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>67</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>86</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>73</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>67</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>93</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>75</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>91</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp092 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>92</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP092</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP092 contributes to ast emp092 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>